--- a/Shared/XLS/Currency.xlsx
+++ b/Shared/XLS/Currency.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
   <si>
     <t>!EnumTable</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -40,59 +40,182 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Ruby</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>골드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다이아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>루비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Gold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Dia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Ruby</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Currency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반적인 재화이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유료 재화이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부분유료 재화이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기 강화 주문서</t>
+  </si>
+  <si>
+    <t>방어구 강화 주문서</t>
+  </si>
+  <si>
+    <t>장신구 강화 주문서</t>
+  </si>
+  <si>
+    <t>승급석</t>
+  </si>
+  <si>
+    <t>마력의 결정</t>
+  </si>
+  <si>
+    <t>계승석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기를 강화하는데 사용한다.</t>
+  </si>
+  <si>
+    <t>방어구를 강화하는데 사용한다.</t>
+  </si>
+  <si>
+    <t>장신구를 강화하는데 사용한다.</t>
+  </si>
+  <si>
+    <t>장비를 승급하는데 사용한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비의 전이에 사용된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_WeaponScroll</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_ArmorScroll</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_AccessoryScroll</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PromotionStone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TransferStone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_TransferStone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponScroll</t>
+  </si>
+  <si>
+    <t>ArmorScroll</t>
+  </si>
+  <si>
+    <t>AccessoryScroll</t>
+  </si>
+  <si>
+    <t>Icon_PromotionStone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MagicCrystal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_MagicCrystal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>청동 열쇠</t>
+  </si>
+  <si>
+    <t>일반 보물 상자를 여는데 사용한다.</t>
+  </si>
+  <si>
+    <t>은 열쇠</t>
+  </si>
+  <si>
+    <t>고급 보물 상자를 여는데 사용한다.</t>
+  </si>
+  <si>
+    <t>금 열쇠</t>
+  </si>
+  <si>
+    <t>최고급 보물 상자를 여는데 사용한다.</t>
+  </si>
+  <si>
+    <t>ItemIcon_BronzeKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_SilverKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_GoldKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BronzeKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SilverKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GoldKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>!Currency</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dia</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ruby</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>골드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>다이아</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>루비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gold</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Gold</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Dia</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Ruby</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Currency</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반적인 재화이다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>유료 재화이다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>부분유료 재화이다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -492,7 +615,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -500,14 +623,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
     <col min="2" max="2" width="15.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.75" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.5" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.25" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.75" style="5" bestFit="1" customWidth="1"/>
@@ -521,7 +644,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
@@ -548,7 +671,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>5</v>
@@ -562,16 +685,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
@@ -581,16 +704,16 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
@@ -600,16 +723,16 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
@@ -618,9 +741,18 @@
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="E7" s="7"/>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
@@ -628,9 +760,18 @@
       <c r="J7" s="7"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="E8" s="7"/>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
@@ -638,9 +779,18 @@
       <c r="J8" s="7"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="E9" s="7"/>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>31</v>
+      </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
@@ -648,15 +798,94 @@
       <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="E10" s="7"/>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
     </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Shared/XLS/Currency.xlsx
+++ b/Shared/XLS/Currency.xlsx
@@ -144,78 +144,78 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>WeaponScroll</t>
+  </si>
+  <si>
+    <t>ArmorScroll</t>
+  </si>
+  <si>
+    <t>AccessoryScroll</t>
+  </si>
+  <si>
+    <t>MagicCrystal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>청동 열쇠</t>
+  </si>
+  <si>
+    <t>일반 보물 상자를 여는데 사용한다.</t>
+  </si>
+  <si>
+    <t>은 열쇠</t>
+  </si>
+  <si>
+    <t>고급 보물 상자를 여는데 사용한다.</t>
+  </si>
+  <si>
+    <t>금 열쇠</t>
+  </si>
+  <si>
+    <t>최고급 보물 상자를 여는데 사용한다.</t>
+  </si>
+  <si>
+    <t>BronzeKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SilverKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GoldKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Currency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_PromotionStone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_MagicCrystal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Icon_TransferStone</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>WeaponScroll</t>
-  </si>
-  <si>
-    <t>ArmorScroll</t>
-  </si>
-  <si>
-    <t>AccessoryScroll</t>
-  </si>
-  <si>
-    <t>Icon_PromotionStone</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MagicCrystal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_MagicCrystal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>청동 열쇠</t>
-  </si>
-  <si>
-    <t>일반 보물 상자를 여는데 사용한다.</t>
-  </si>
-  <si>
-    <t>은 열쇠</t>
-  </si>
-  <si>
-    <t>고급 보물 상자를 여는데 사용한다.</t>
-  </si>
-  <si>
-    <t>금 열쇠</t>
-  </si>
-  <si>
-    <t>최고급 보물 상자를 여는데 사용한다.</t>
-  </si>
-  <si>
-    <t>ItemIcon_BronzeKey</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemIcon_SilverKey</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemIcon_GoldKey</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BronzeKey</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SilverKey</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GoldKey</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dia</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Currency</t>
+    <t>Icon_BronzeKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_SilverKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_GoldKey</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -615,7 +615,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -671,7 +671,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>5</v>
@@ -704,7 +704,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>8</v>
@@ -742,7 +742,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>18</v>
@@ -761,7 +761,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>19</v>
@@ -780,7 +780,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>20</v>
@@ -808,7 +808,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
@@ -818,7 +818,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>22</v>
@@ -827,7 +827,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -841,49 +841,49 @@
         <v>28</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
